--- a/artfynd/A 31622-2021 artfynd.xlsx
+++ b/artfynd/A 31622-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31622-2021 artfynd.xlsx
+++ b/artfynd/A 31622-2021 artfynd.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Annika Rastén, Johan Allmér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 31622-2021 artfynd.xlsx
+++ b/artfynd/A 31622-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121783009</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
